--- a/data/trans_dic/P3A_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -649,62 +649,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>79,59%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>22,59; 29,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>35,69; 43,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>43,96; 51,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,26</t>
+          <t>58,56; 67,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>80,81; 86,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>81,49; 86,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>84,09; 89,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,15</t>
+          <t>91,94; 95,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,14</t>
+          <t>52,07; 57,42</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,14</t>
+          <t>59,09; 64,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,15</t>
+          <t>64,73; 69,82</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>76,71; 82,2</t>
         </is>
       </c>
     </row>
@@ -789,62 +789,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>69,84%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,21</t>
+          <t>28,24; 34,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,21</t>
+          <t>38,95; 45,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>48,2; 54,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>24,87; 66,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,21</t>
+          <t>83,7; 88,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>80,0; 85,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>86,97; 91,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,13</t>
+          <t>90,28; 93,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,11</t>
+          <t>56,51; 61,23</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>60,47; 64,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>68,33; 72,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,08</t>
+          <t>47,28; 79,42</t>
         </is>
       </c>
     </row>
@@ -929,62 +929,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>82,28%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,3</t>
+          <t>35,48; 43,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>39,66; 47,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>48,32; 55,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>63,45; 71,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>84,39; 89,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,27</t>
+          <t>82,5; 87,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,26</t>
+          <t>85,81; 90,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,18</t>
+          <t>90,3; 96,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,14</t>
+          <t>60,75; 65,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,14</t>
+          <t>61,89; 67,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,13</t>
+          <t>68,3; 73,02</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,11</t>
+          <t>78,69; 88,24</t>
         </is>
       </c>
     </row>
@@ -1069,62 +1069,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>78,48%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>36,15; 42,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,21</t>
+          <t>44,86; 51,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,21</t>
+          <t>56,04; 62,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>63,59; 70,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>78,04; 82,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>80,25; 84,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>82,95; 87,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>85,57; 90,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>58,58; 62,9</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>64,29; 68,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>71,17; 75,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,07</t>
+          <t>76,36; 81,34</t>
         </is>
       </c>
     </row>
@@ -1209,62 +1209,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>76,96%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>32,51; 35,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>41,96; 45,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>51,22; 54,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>46,73; 66,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>82,71; 85,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>82,28; 84,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>86,21; 88,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,04</t>
+          <t>90,37; 93,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,03</t>
+          <t>58,32; 60,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,03</t>
+          <t>62,82; 65,2</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,03</t>
+          <t>69,55; 71,68</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,02</t>
+          <t>68,12; 80,32</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1509,62 +1509,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>174</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>260</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>306</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>475</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>579</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>546</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>580</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>753</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>806</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>886</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1627</t>
         </is>
       </c>
     </row>
@@ -1577,62 +1577,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>180024</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>279446</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>322538</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>401782</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>575933</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>587494</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>584346</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>680879</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>755957</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>866940</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>906884</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1082661</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1948</t>
+          <t>156801; 206413</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2001</t>
+          <t>251067; 304636</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1984</t>
+          <t>296666; 347631</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 1670</t>
+          <t>371840; 428157</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1896</t>
+          <t>555359; 593353</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2056</t>
+          <t>568035; 604303</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1937</t>
+          <t>564985; 599797</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1122</t>
+          <t>666884; 692062</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1924</t>
+          <t>719230; 793101</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 2030</t>
+          <t>827546; 905328</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 1962</t>
+          <t>871669; 940327</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 1325</t>
+          <t>1043492; 1118120</t>
         </is>
       </c>
     </row>
@@ -1717,62 +1717,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>271</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>397</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>479</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>624</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>775</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>775</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>872</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1411</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2035</t>
         </is>
       </c>
     </row>
@@ -1785,62 +1785,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>302065</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>430310</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>524221</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>619109</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>832484</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>852026</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>929024</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>883438</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1134549</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1282336</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1453245</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1502548</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2059</t>
+          <t>271654; 332508</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2086</t>
+          <t>396123; 461838</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2063</t>
+          <t>492302; 556237</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2374</t>
+          <t>296623; 791176</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2046</t>
+          <t>810546; 854216</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2106</t>
+          <t>825744; 877635</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2048</t>
+          <t>906187; 949307</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 1213</t>
+          <t>865503; 898428</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 2054</t>
+          <t>1090750; 1181813</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 2098</t>
+          <t>1239062; 1326955</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2056</t>
+          <t>1410036; 1496392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 1665</t>
+          <t>1017286; 1708633</t>
         </is>
       </c>
     </row>
@@ -1925,62 +1925,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>241</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>296</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>359</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>461</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>602</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>601</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>649</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>972</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>843</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>897</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1433</t>
         </is>
       </c>
     </row>
@@ -1993,62 +1993,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>268029</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>328409</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>394431</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>477663</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>592388</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>661074</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>691528</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>870118</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>860417</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>989483</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1085959</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1347781</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2029</t>
+          <t>240764; 294711</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2108</t>
+          <t>300437; 361473</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2091</t>
+          <t>365176; 422987</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1999</t>
+          <t>447112; 507257</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1883</t>
+          <t>574226; 608597</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2114</t>
+          <t>639511; 681857</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2046</t>
+          <t>671908; 708477</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 1710</t>
+          <t>842797; 904586</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 1955</t>
+          <t>825543; 896336</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 2113</t>
+          <t>948692; 1027058</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2069</t>
+          <t>1050873; 1123556</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 1825</t>
+          <t>1289041; 1445410</t>
         </is>
       </c>
     </row>
@@ -2133,62 +2133,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>373</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>440</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>550</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>667</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>801</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>829</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>821</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2069</t>
         </is>
       </c>
     </row>
@@ -2201,62 +2201,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>370218</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>457676</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>557284</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>622054</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>836481</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>870227</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>888469</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>963142</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1206699</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1327903</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1445753</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1585195</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1819</t>
+          <t>340271; 401739</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1998</t>
+          <t>425181; 490351</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1929</t>
+          <t>523024; 585952</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 1768</t>
+          <t>588974; 652798</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1998</t>
+          <t>810529; 861895</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2012</t>
+          <t>844167; 891483</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2088</t>
+          <t>864994; 912160</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 1346</t>
+          <t>935813; 990670</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1910</t>
+          <t>1159868; 1245296</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 2006</t>
+          <t>1285571; 1370868</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 2011</t>
+          <t>1406466; 1486032</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 1512</t>
+          <t>1542309; 1643001</t>
         </is>
       </c>
     </row>
@@ -2341,62 +2341,62 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1694</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4937</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4144</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7164</t>
         </is>
       </c>
     </row>
@@ -2409,62 +2409,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1120336</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1495841</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1798474</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2120608</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2837285</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2970821</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3093366</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3397577</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3957622</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4466662</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4891842</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5518185</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1957</t>
+          <t>1064943; 1177799</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2050</t>
+          <t>1437310; 1559799</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2017</t>
+          <t>1734100; 1856067</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1968</t>
+          <t>1616269; 2302431</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 1968</t>
+          <t>2791090; 2877241</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2072</t>
+          <t>2926098; 3019903</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 2039</t>
+          <t>3051482; 3135285</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 1328</t>
+          <t>3353826; 3455773</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 1963</t>
+          <t>3878149; 4043597</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 2062</t>
+          <t>4386140; 4552176</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 2028</t>
+          <t>4816483; 4963963</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 1576</t>
+          <t>4883769; 5758566</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>78,46%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,59; 29,74</t>
+          <t>23,0; 29,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,69; 43,3</t>
+          <t>35,89; 43,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43,96; 51,52</t>
+          <t>44,17; 51,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58,56; 67,43</t>
+          <t>58,57; 66,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>80,81; 86,34</t>
+          <t>81,07; 86,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,49; 86,69</t>
+          <t>81,34; 86,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,09; 89,27</t>
+          <t>84,34; 89,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>91,94; 95,41</t>
+          <t>91,23; 94,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52,07; 57,42</t>
+          <t>52,34; 57,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59,09; 64,64</t>
+          <t>59,47; 64,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64,73; 69,82</t>
+          <t>65,05; 70,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76,71; 82,2</t>
+          <t>75,73; 80,65</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>78,62%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,24; 34,57</t>
+          <t>28,55; 34,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38,95; 45,42</t>
+          <t>39,23; 45,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48,2; 54,46</t>
+          <t>47,73; 54,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,87; 66,33</t>
+          <t>61,44; 68,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,7; 88,21</t>
+          <t>83,61; 88,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,0; 85,03</t>
+          <t>79,96; 85,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,97; 91,11</t>
+          <t>86,94; 91,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>90,28; 93,72</t>
+          <t>89,91; 93,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>56,51; 61,23</t>
+          <t>56,63; 61,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60,47; 64,76</t>
+          <t>60,47; 64,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68,33; 72,52</t>
+          <t>68,19; 72,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>47,28; 79,42</t>
+          <t>76,62; 80,47</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>79,21%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,48; 43,44</t>
+          <t>35,58; 43,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,66; 47,71</t>
+          <t>39,7; 47,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48,32; 55,97</t>
+          <t>47,63; 55,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>63,45; 71,98</t>
+          <t>63,65; 71,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>84,39; 89,44</t>
+          <t>84,31; 89,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82,5; 87,96</t>
+          <t>82,2; 87,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,81; 90,48</t>
+          <t>85,89; 90,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>90,3; 96,92</t>
+          <t>87,92; 92,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>60,75; 65,96</t>
+          <t>60,7; 65,94</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>61,89; 67,01</t>
+          <t>61,8; 67,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68,3; 73,02</t>
+          <t>68,12; 72,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>78,69; 88,24</t>
+          <t>76,5; 81,56</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>77,56%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,15; 42,68</t>
+          <t>36,27; 42,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,86; 51,74</t>
+          <t>45,0; 52,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56,04; 62,78</t>
+          <t>56,51; 63,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63,59; 70,48</t>
+          <t>62,92; 69,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>78,04; 82,99</t>
+          <t>77,98; 82,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,25; 84,75</t>
+          <t>80,35; 85,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,95; 87,48</t>
+          <t>82,61; 87,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>85,57; 90,58</t>
+          <t>85,44; 89,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>58,58; 62,9</t>
+          <t>58,76; 62,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64,29; 68,56</t>
+          <t>64,19; 68,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71,17; 75,2</t>
+          <t>71,22; 75,05</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>76,36; 81,34</t>
+          <t>75,53; 79,34</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>78,41%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>32,51; 35,96</t>
+          <t>32,5; 35,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41,96; 45,53</t>
+          <t>41,96; 45,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51,22; 54,83</t>
+          <t>51,19; 54,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46,73; 66,57</t>
+          <t>63,75; 67,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>82,71; 85,26</t>
+          <t>82,87; 85,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,28; 84,92</t>
+          <t>82,2; 84,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,21; 88,58</t>
+          <t>86,31; 88,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>90,37; 93,12</t>
+          <t>89,56; 91,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>58,32; 60,8</t>
+          <t>58,33; 60,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62,82; 65,2</t>
+          <t>62,81; 65,2</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69,55; 71,68</t>
+          <t>69,58; 71,79</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>68,12; 80,32</t>
+          <t>77,31; 79,47</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>401782</t>
+          <t>432141</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>680879</t>
+          <t>685471</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1082661</t>
+          <t>1117612</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>156801; 206413</t>
+          <t>159613; 204099</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>251067; 304636</t>
+          <t>252441; 305688</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>296666; 347631</t>
+          <t>298031; 348530</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>371840; 428157</t>
+          <t>404275; 458547</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>555359; 593353</t>
+          <t>557099; 593219</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>568035; 604303</t>
+          <t>566985; 605136</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>564985; 599797</t>
+          <t>566662; 601249</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>666884; 692062</t>
+          <t>669777; 695963</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>719230; 793101</t>
+          <t>722857; 794488</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>827546; 905328</t>
+          <t>832937; 905471</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>871669; 940327</t>
+          <t>876044; 945033</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1043492; 1118120</t>
+          <t>1078691; 1148761</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>619109</t>
+          <t>681901</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>883438</t>
+          <t>985056</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1502548</t>
+          <t>1666957</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>271654; 332508</t>
+          <t>274582; 334785</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>396123; 461838</t>
+          <t>398929; 465165</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>492302; 556237</t>
+          <t>487496; 554290</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>296623; 791176</t>
+          <t>644439; 716147</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>810546; 854216</t>
+          <t>809656; 853375</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>825744; 877635</t>
+          <t>825366; 877506</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>906187; 949307</t>
+          <t>905842; 949390</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>865503; 898428</t>
+          <t>963321; 1002231</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1090750; 1181813</t>
+          <t>1093021; 1186617</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1239062; 1326955</t>
+          <t>1239136; 1330499</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1410036; 1496392</t>
+          <t>1406975; 1494837</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1017286; 1708633</t>
+          <t>1624680; 1706175</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>477663</t>
+          <t>542863</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>870118</t>
+          <t>736714</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1347781</t>
+          <t>1279576</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>240764; 294711</t>
+          <t>241422; 294727</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>300437; 361473</t>
+          <t>300768; 357683</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>365176; 422987</t>
+          <t>359957; 420043</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>447112; 507257</t>
+          <t>511170; 572086</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>574226; 608597</t>
+          <t>573706; 607827</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>639511; 681857</t>
+          <t>637160; 680831</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>671908; 708477</t>
+          <t>672528; 708543</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>842797; 904586</t>
+          <t>714114; 754309</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>825543; 896336</t>
+          <t>824855; 896081</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>948692; 1027058</t>
+          <t>947331; 1028937</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1050873; 1123556</t>
+          <t>1048210; 1120240</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1289041; 1445410</t>
+          <t>1235786; 1317392</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>622054</t>
+          <t>655652</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>963142</t>
+          <t>978683</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1585195</t>
+          <t>1634336</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>340271; 401739</t>
+          <t>341385; 398890</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>425181; 490351</t>
+          <t>426500; 494160</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>523024; 585952</t>
+          <t>527404; 589717</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>588974; 652798</t>
+          <t>622570; 685474</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>810529; 861895</t>
+          <t>809867; 859809</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>844167; 891483</t>
+          <t>845185; 895962</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>864994; 912160</t>
+          <t>861429; 911542</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>935813; 990670</t>
+          <t>955018; 1001245</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1159868; 1245296</t>
+          <t>1163397; 1247229</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1285571; 1370868</t>
+          <t>1283575; 1370558</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1406466; 1486032</t>
+          <t>1407470; 1482975</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1542309; 1643001</t>
+          <t>1591504; 1671898</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2120608</t>
+          <t>2312557</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3397577</t>
+          <t>3385923</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5518185</t>
+          <t>5698481</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1064943; 1177799</t>
+          <t>1064692; 1178098</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1437310; 1559799</t>
+          <t>1437562; 1557613</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1734100; 1856067</t>
+          <t>1732899; 1853887</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1616269; 2302431</t>
+          <t>2251481; 2374350</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2791090; 2877241</t>
+          <t>2796494; 2881418</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2926098; 3019903</t>
+          <t>2923419; 3017987</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3051482; 3135285</t>
+          <t>3055023; 3134357</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3353826; 3455773</t>
+          <t>3345644; 3421280</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3878149; 4043597</t>
+          <t>3879112; 4037308</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4386140; 4552176</t>
+          <t>4385240; 4552131</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4816483; 4963963</t>
+          <t>4818389; 4971138</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4883769; 5758566</t>
+          <t>5618246; 5775071</t>
         </is>
       </c>
     </row>
